--- a/Hardware/Basic/novus_t1200xe_0.8_pa_basic_cpl_smd.xlsx
+++ b/Hardware/Basic/novus_t1200xe_0.8_pa_basic_cpl_smd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Documents\EAGLE\Toshiba-T1200xe-PSU\jlcpcb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC58570A-DC5C-40F7-8DD3-912E26BF492F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9B0D88-7C8D-4D5A-88B3-4E9CAE217D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD71A3F3-122F-4538-AFBB-0221CFE0CCFD}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">novus_t1200xe_pm_dual_d8_top!$A$1:$E$101</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">novus_t1200xe_pm_dual_d8_top!$A$1:$E$102</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="257">
   <si>
     <t>DESIGNATOR</t>
   </si>
@@ -802,6 +802,12 @@
   </si>
   <si>
     <t>58.01</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>78.79</t>
   </si>
 </sst>
 </file>
@@ -900,10 +906,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F5B8B740-98D2-4FB2-9D76-56D056A43C93}" name="novus_t1200xe_pm_dual_d8_top" displayName="novus_t1200xe_pm_dual_d8_top" ref="A1:E101" tableType="queryTable" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E101" xr:uid="{F5B8B740-98D2-4FB2-9D76-56D056A43C93}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E101">
-    <sortCondition ref="A1:A101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F5B8B740-98D2-4FB2-9D76-56D056A43C93}" name="novus_t1200xe_pm_dual_d8_top" displayName="novus_t1200xe_pm_dual_d8_top" ref="A1:E102" tableType="queryTable" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E102" xr:uid="{F5B8B740-98D2-4FB2-9D76-56D056A43C93}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E102">
+    <sortCondition ref="A1:A102"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{5CC18910-9929-4325-BE80-B9E8EA6E35CA}" uniqueName="1" name="DESIGNATOR" queryTableFieldId="1" dataDxfId="4"/>
@@ -1213,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51A65530-6866-4DA0-85DF-598417E6A878}">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -2891,16 +2897,16 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>240</v>
+        <v>38</v>
       </c>
       <c r="D99" s="1">
-        <v>180</v>
+        <v>315</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>5</v>
@@ -2908,16 +2914,16 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>46</v>
+        <v>239</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="D100" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>5</v>
@@ -2925,18 +2931,35 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D101" s="1">
+        <v>0</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D101" s="1">
+      <c r="D102" s="1">
         <v>225</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>5</v>
       </c>
     </row>
